--- a/ksoft/docs/records/Carrier_Records.xlsx
+++ b/ksoft/docs/records/Carrier_Records.xlsx
@@ -14280,13 +14280,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D724B617-4C33-4A80-AA43-918FEB20EC0F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{308D3AFC-1124-419F-9C6C-C4D69F0302E1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A27D425-CC2C-4128-A6C6-6C1EC3595D36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CA0275-9309-4E65-BDD5-1C7EF39E113C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C01EE30-E3DC-4CBF-875B-76E6B3BFAF59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D7012B-97B2-4B7D-ACB8-2FE12EF971B1}"/>
 </file>
--- a/ksoft/docs/records/Carrier_Records.xlsx
+++ b/ksoft/docs/records/Carrier_Records.xlsx
@@ -14280,13 +14280,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{308D3AFC-1124-419F-9C6C-C4D69F0302E1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D724B617-4C33-4A80-AA43-918FEB20EC0F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29CA0275-9309-4E65-BDD5-1C7EF39E113C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A27D425-CC2C-4128-A6C6-6C1EC3595D36}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58D7012B-97B2-4B7D-ACB8-2FE12EF971B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C01EE30-E3DC-4CBF-875B-76E6B3BFAF59}"/>
 </file>